--- a/data/trans_orig/IP07A15-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A15-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2007 (tasa de respuesta: 98,9%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2007 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25362</t>
+          <t>25679</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30043</t>
+          <t>29754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45123</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27714</t>
+          <t>27719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>12611</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22910</t>
+          <t>22792</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32344</t>
+          <t>32379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46748</t>
+          <t>47219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,75%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>16342</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17962</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20187</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32769</t>
+          <t>32543</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,38%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10571</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>19679</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>8920</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>18240</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22647</t>
+          <t>22211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35042</t>
+          <t>34817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,11%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30874</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33213</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46970</t>
+          <t>47636</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,78%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16548</t>
+          <t>16847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>16241</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>28354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26415</t>
+          <t>26723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41424</t>
+          <t>42547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9680</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36339</t>
+          <t>35956</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52215</t>
+          <t>50954</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33304</t>
+          <t>34300</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49206</t>
+          <t>49520</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75346</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97656</t>
+          <t>97632</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,96%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28692</t>
+          <t>28961</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44042</t>
+          <t>43945</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33653</t>
+          <t>33743</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49812</t>
+          <t>48437</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66459</t>
+          <t>66445</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>87349</t>
+          <t>87990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15538</t>
+          <t>16113</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23131</t>
+          <t>24702</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24891</t>
+          <t>24863</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36120</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28469</t>
+          <t>28620</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41733</t>
+          <t>42081</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56656</t>
+          <t>56605</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>73727</t>
+          <t>74828</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>60,36%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>11795</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22667</t>
+          <t>22958</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>19395</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32524</t>
+          <t>32086</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>34727</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>52213</t>
+          <t>52237</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20695</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>14590</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>25150</t>
+          <t>25647</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13936</t>
+          <t>13686</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23425</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31655</t>
+          <t>31729</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45544</t>
+          <t>45595</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14006</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24623</t>
+          <t>24641</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>18236</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>26467</t>
+          <t>26525</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>40938</t>
+          <t>40601</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>126931</t>
+          <t>126104</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>154280</t>
+          <t>153202</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>138902</t>
+          <t>139728</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>168854</t>
+          <t>169137</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>272624</t>
+          <t>272928</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>314086</t>
+          <t>313317</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,67%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>108679</t>
+          <t>108868</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>135782</t>
+          <t>135983</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>120203</t>
+          <t>118613</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>147178</t>
+          <t>147257</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>236188</t>
+          <t>236526</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>276355</t>
+          <t>278120</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>22127</t>
+          <t>21604</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>38687</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>26426</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>44848</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>53371</t>
+          <t>50746</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>76587</t>
+          <t>76101</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2012 (tasa de respuesta: 97,71%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2012 (tasa de respuesta: 97,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21301</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20923</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>25035</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39299</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,42%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14293</t>
+          <t>13949</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24895</t>
+          <t>24305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19890</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26841</t>
+          <t>27507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41586</t>
+          <t>41927</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>10834</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13967</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23390</t>
+          <t>23864</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27954</t>
+          <t>27564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41310</t>
+          <t>40807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,45%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>20524</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>18693</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>23086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35580</t>
+          <t>35684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>11793</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>13977</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22107</t>
+          <t>22680</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30284</t>
+          <t>30625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44297</t>
+          <t>45210</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>59,72%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>14222</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25281</t>
+          <t>25538</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37676</t>
+          <t>37220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13264</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46755</t>
+          <t>46633</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61776</t>
+          <t>61754</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45803</t>
+          <t>46198</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62541</t>
+          <t>62143</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97417</t>
+          <t>98310</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119135</t>
+          <t>119950</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,48%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17280</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31759</t>
+          <t>31358</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45138</t>
+          <t>45492</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51380</t>
+          <t>50700</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71964</t>
+          <t>72161</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10862</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>19362</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37646</t>
+          <t>37931</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51954</t>
+          <t>51210</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27615</t>
+          <t>27465</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41054</t>
+          <t>41228</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>67708</t>
+          <t>68338</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>88390</t>
+          <t>89065</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,98%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t>25227</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23009</t>
+          <t>22061</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36355</t>
+          <t>36177</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>38850</t>
+          <t>38941</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57544</t>
+          <t>58175</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24873</t>
+          <t>24589</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>18446</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26721</t>
+          <t>26539</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>29780</t>
+          <t>30524</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42896</t>
+          <t>43143</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27707</t>
+          <t>27543</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>150475</t>
+          <t>150211</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>177321</t>
+          <t>179019</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>148907</t>
+          <t>148319</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>176856</t>
+          <t>176757</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>306497</t>
+          <t>305959</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>347375</t>
+          <t>345894</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,31%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>92776</t>
+          <t>92737</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>120030</t>
+          <t>120581</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>104560</t>
+          <t>105806</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>132322</t>
+          <t>132469</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>207105</t>
+          <t>206039</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>245867</t>
+          <t>246510</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>24250</t>
+          <t>23877</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>41638</t>
+          <t>42107</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>31823</t>
+          <t>32478</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>44925</t>
+          <t>45590</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>69434</t>
+          <t>67895</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15468</t>
+          <t>15823</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>25072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15616</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26143</t>
+          <t>25873</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33680</t>
+          <t>34045</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48087</t>
+          <t>48102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15199</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20649</t>
+          <t>20815</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>18354</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33122</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>43,62%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12062</t>
+          <t>11860</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18114</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30301</t>
+          <t>30292</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19638</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31232</t>
+          <t>31412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41331</t>
+          <t>41163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57321</t>
+          <t>57640</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27605</t>
+          <t>27419</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30593</t>
+          <t>30507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46959</t>
+          <t>47252</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16476</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10409</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15450</t>
+          <t>15902</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26293</t>
+          <t>26395</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28892</t>
+          <t>29382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42300</t>
+          <t>42535</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11191</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21603</t>
+          <t>21532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19951</t>
+          <t>19746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33378</t>
+          <t>32527</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51552</t>
+          <t>51678</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69440</t>
+          <t>68462</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48659</t>
+          <t>49135</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66351</t>
+          <t>66321</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>106389</t>
+          <t>106171</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>130898</t>
+          <t>130597</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,73%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32971</t>
+          <t>33507</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49870</t>
+          <t>49858</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32530</t>
+          <t>32558</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>49597</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70709</t>
+          <t>69729</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94687</t>
+          <t>93200</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>22965</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>716</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37379</t>
+          <t>37307</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51045</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33615</t>
+          <t>32588</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47679</t>
+          <t>46870</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>74819</t>
+          <t>75076</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>95594</t>
+          <t>95406</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,41%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19295</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33239</t>
+          <t>32367</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>17393</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30466</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>39880</t>
+          <t>39289</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59898</t>
+          <t>58980</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17814</t>
+          <t>18288</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10755</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20222</t>
+          <t>20090</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>14036</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24509</t>
+          <t>24064</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>27435</t>
+          <t>27723</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>41829</t>
+          <t>41470</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,65%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18814</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19043</t>
+          <t>18457</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>21352</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35074</t>
+          <t>35365</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>569</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>164335</t>
+          <t>163835</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>194720</t>
+          <t>194754</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>169779</t>
+          <t>170405</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>199726</t>
+          <t>200542</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>343856</t>
+          <t>341821</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>385766</t>
+          <t>387030</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>107308</t>
+          <t>106454</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>138038</t>
+          <t>137486</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>111371</t>
+          <t>111779</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>140007</t>
+          <t>140890</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>227866</t>
+          <t>228391</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>269133</t>
+          <t>270308</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>22306</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>40231</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>34685</t>
+          <t>34719</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>45263</t>
+          <t>45310</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>68408</t>
+          <t>69098</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>14589</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
